--- a/business-libraries/test-data/home_school/output_template.xlsx
+++ b/business-libraries/test-data/home_school/output_template.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -424,22 +424,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>TPL-HS-RED-SUMMARY</v>
+        <v>HOME_SCHOOL_TPL_E_SUMMARY</v>
       </c>
       <c r="B2" t="str">
         <v>home_school</v>
       </c>
       <c r="C2" t="str">
-        <v>red</v>
+        <v>E</v>
       </c>
       <c r="D2" t="str">
         <v>summary</v>
       </c>
       <c r="E2" t="str">
-        <v>评估显示，您在「${维度名1}」和「${维度名2}」两个维度上的得分同时处于高危水平。沟通质量与信任双低，需要优先关注。</v>
+        <v>本次评估触发 E 级保护通道，核心问题是「${主要归因}」。请立即停止单独沟通，保存全部记录并当天上报年级组长，后续由学校层面承接。</v>
       </c>
       <c r="F2" t="str">
-        <v>${维度名1} ${维度名2} 会被替换为实际触发红线的维度中文名</v>
+        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
       </c>
       <c r="G2" t="str">
         <v>1</v>
@@ -447,22 +447,22 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>TPL-HS-RED-CONCLUSION</v>
+        <v>HOME_SCHOOL_TPL_D_SUMMARY</v>
       </c>
       <c r="B3" t="str">
         <v>home_school</v>
       </c>
       <c r="C3" t="str">
-        <v>red</v>
+        <v>D</v>
       </c>
       <c r="D3" t="str">
-        <v>conclusion</v>
+        <v>summary</v>
       </c>
       <c r="E3" t="str">
-        <v>本次评估结论：${主归因}（${次归因}）。已触发安全熔断，常规建议暂停输出。</v>
+        <v>本次沟通风险等级为 D 级，主要归因是「${主要归因}」，同时需关注「${次要归因}」。建议由年级组长陪同沟通并全程留痕。</v>
       </c>
       <c r="F3" t="str">
-        <v>${主归因} 来自归因-分级规则.主归因；${次归因} 来自归因-分级规则.次归因</v>
+        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
       </c>
       <c r="G3" t="str">
         <v>2</v>
@@ -470,22 +470,22 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>TPL-HS-RED-GOAL</v>
+        <v>HOME_SCHOOL_TPL_C_SUMMARY</v>
       </c>
       <c r="B4" t="str">
         <v>home_school</v>
       </c>
       <c r="C4" t="str">
-        <v>red</v>
+        <v>C</v>
       </c>
       <c r="D4" t="str">
-        <v>goal</v>
+        <v>summary</v>
       </c>
       <c r="E4" t="str">
-        <v>当前首要目标：1) 确保教师获得即时心理支持 2) 降低当前的急性压力水平 3) 建立至少一个可依赖的支持关系</v>
+        <v>本次评估提示沟通存在明显阻力，核心变量是「${主要归因}」。处理重点不是先说服家长，而是先稳住情绪和事实边界，再决定沟通节奏。</v>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
       </c>
       <c r="G4" t="str">
         <v>3</v>
@@ -493,22 +493,22 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>TPL-HS-ORANGE-ATTRIBUTION</v>
+        <v>HOME_SCHOOL_TPL_B_SUMMARY</v>
       </c>
       <c r="B5" t="str">
         <v>home_school</v>
       </c>
       <c r="C5" t="str">
-        <v>orange</v>
+        <v>B</v>
       </c>
       <c r="D5" t="str">
-        <v>attribution</v>
+        <v>summary</v>
       </c>
       <c r="E5" t="str">
-        <v>本次评估的归因分析：${主归因}。建议重点关注以下方面：${工具标签}</v>
+        <v>本次评估显示沟通前需要一定铺垫，主要落在「${主要归因}」。建议先修复关系容器，积累两到三次正向接触后再谈具体问题。</v>
       </c>
       <c r="F5" t="str">
-        <v>${主归因} ${工具标签} 从归因规则中取值</v>
+        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
       </c>
       <c r="G5" t="str">
         <v>4</v>
@@ -516,53 +516,30 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>TPL-HS-ORANGE-ACTION</v>
+        <v>HOME_SCHOOL_TPL_A_SUMMARY</v>
       </c>
       <c r="B6" t="str">
         <v>home_school</v>
       </c>
       <c r="C6" t="str">
-        <v>orange</v>
+        <v>A</v>
       </c>
       <c r="D6" t="str">
-        <v>action</v>
+        <v>summary</v>
       </c>
       <c r="E6" t="str">
-        <v>根据评估结果，建议采取以下行动：${输出动作摘要}。推荐工具：${输出工具摘要}。</v>
+        <v>当前家校关系状况良好，可按常规节奏沟通。保持日常的正向接触，让关系容器持续有储备。</v>
       </c>
       <c r="F6" t="str">
-        <v>${输出动作摘要} ${输出工具摘要} 从归因规则中取值</v>
+        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
       </c>
       <c r="G6" t="str">
         <v>5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>TPL-HS-GREEN-SUMMARY</v>
-      </c>
-      <c r="B7" t="str">
-        <v>home_school</v>
-      </c>
-      <c r="C7" t="str">
-        <v>green</v>
-      </c>
-      <c r="D7" t="str">
-        <v>summary</v>
-      </c>
-      <c r="E7" t="str">
-        <v>本次评估结果整体良好，各项指标均在正常范围内。继续保持现有节奏。</v>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/business-libraries/test-data/home_school/output_template.xlsx
+++ b/business-libraries/test-data/home_school/output_template.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -424,13 +424,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>HOME_SCHOOL_TPL_E_SUMMARY</v>
+        <v>TPL_HS_RED_1</v>
       </c>
       <c r="B2" t="str">
         <v>home_school</v>
       </c>
       <c r="C2" t="str">
-        <v>E</v>
+        <v>red</v>
       </c>
       <c r="D2" t="str">
         <v>summary</v>
@@ -439,7 +439,7 @@
         <v>本次评估触发 E 级保护通道，核心问题是「${主要归因}」。请立即停止单独沟通，保存全部记录并当天上报年级组长，后续由学校层面承接。</v>
       </c>
       <c r="F2" t="str">
-        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
+        <v>可用占位符见 ⑩ 说明</v>
       </c>
       <c r="G2" t="str">
         <v>1</v>
@@ -447,13 +447,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>HOME_SCHOOL_TPL_D_SUMMARY</v>
+        <v>TPL_HS_ORANGE_2</v>
       </c>
       <c r="B3" t="str">
         <v>home_school</v>
       </c>
       <c r="C3" t="str">
-        <v>D</v>
+        <v>orange</v>
       </c>
       <c r="D3" t="str">
         <v>summary</v>
@@ -462,7 +462,7 @@
         <v>本次沟通风险等级为 D 级，主要归因是「${主要归因}」，同时需关注「${次要归因}」。建议由年级组长陪同沟通并全程留痕。</v>
       </c>
       <c r="F3" t="str">
-        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
+        <v>可用占位符见 ⑩ 说明</v>
       </c>
       <c r="G3" t="str">
         <v>2</v>
@@ -470,13 +470,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>HOME_SCHOOL_TPL_C_SUMMARY</v>
+        <v>TPL_HS_YELLOW_3</v>
       </c>
       <c r="B4" t="str">
         <v>home_school</v>
       </c>
       <c r="C4" t="str">
-        <v>C</v>
+        <v>yellow</v>
       </c>
       <c r="D4" t="str">
         <v>summary</v>
@@ -485,7 +485,7 @@
         <v>本次评估提示沟通存在明显阻力，核心变量是「${主要归因}」。处理重点不是先说服家长，而是先稳住情绪和事实边界，再决定沟通节奏。</v>
       </c>
       <c r="F4" t="str">
-        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
+        <v>可用占位符见 ⑩ 说明</v>
       </c>
       <c r="G4" t="str">
         <v>3</v>
@@ -493,53 +493,30 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>HOME_SCHOOL_TPL_B_SUMMARY</v>
+        <v>TPL_HS_DEFAULT</v>
       </c>
       <c r="B5" t="str">
         <v>home_school</v>
       </c>
       <c r="C5" t="str">
-        <v>B</v>
+        <v>green</v>
       </c>
       <c r="D5" t="str">
         <v>summary</v>
       </c>
       <c r="E5" t="str">
-        <v>本次评估显示沟通前需要一定铺垫，主要落在「${主要归因}」。建议先修复关系容器，积累两到三次正向接触后再谈具体问题。</v>
+        <v>当前家校关系状况良好，可按常规节奏沟通。保持日常的正向接触，让角色边界持续有储备。</v>
       </c>
       <c r="F5" t="str">
-        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
+        <v>兜底模板：命中未覆盖等级时使用</v>
       </c>
       <c r="G5" t="str">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>HOME_SCHOOL_TPL_A_SUMMARY</v>
-      </c>
-      <c r="B6" t="str">
-        <v>home_school</v>
-      </c>
-      <c r="C6" t="str">
-        <v>A</v>
-      </c>
-      <c r="D6" t="str">
-        <v>summary</v>
-      </c>
-      <c r="E6" t="str">
-        <v>当前家校关系状况良好，可按常规节奏沟通。保持日常的正向接触，让关系容器持续有储备。</v>
-      </c>
-      <c r="F6" t="str">
-        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
-      </c>
-      <c r="G6" t="str">
-        <v>5</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/business-libraries/test-data/home_school/output_template.xlsx
+++ b/business-libraries/test-data/home_school/output_template.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -424,13 +424,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>TPL_HS_RED_1</v>
+        <v>HOME_SCHOOL_TPL_E_SUMMARY</v>
       </c>
       <c r="B2" t="str">
         <v>home_school</v>
       </c>
       <c r="C2" t="str">
-        <v>red</v>
+        <v>E</v>
       </c>
       <c r="D2" t="str">
         <v>summary</v>
@@ -439,7 +439,7 @@
         <v>本次评估触发 E 级保护通道，核心问题是「${主要归因}」。请立即停止单独沟通，保存全部记录并当天上报年级组长，后续由学校层面承接。</v>
       </c>
       <c r="F2" t="str">
-        <v>可用占位符见 ⑩ 说明</v>
+        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
       </c>
       <c r="G2" t="str">
         <v>1</v>
@@ -447,13 +447,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>TPL_HS_ORANGE_2</v>
+        <v>HOME_SCHOOL_TPL_D_SUMMARY</v>
       </c>
       <c r="B3" t="str">
         <v>home_school</v>
       </c>
       <c r="C3" t="str">
-        <v>orange</v>
+        <v>D</v>
       </c>
       <c r="D3" t="str">
         <v>summary</v>
@@ -462,7 +462,7 @@
         <v>本次沟通风险等级为 D 级，主要归因是「${主要归因}」，同时需关注「${次要归因}」。建议由年级组长陪同沟通并全程留痕。</v>
       </c>
       <c r="F3" t="str">
-        <v>可用占位符见 ⑩ 说明</v>
+        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
       </c>
       <c r="G3" t="str">
         <v>2</v>
@@ -470,13 +470,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>TPL_HS_YELLOW_3</v>
+        <v>HOME_SCHOOL_TPL_C_SUMMARY</v>
       </c>
       <c r="B4" t="str">
         <v>home_school</v>
       </c>
       <c r="C4" t="str">
-        <v>yellow</v>
+        <v>C</v>
       </c>
       <c r="D4" t="str">
         <v>summary</v>
@@ -485,7 +485,7 @@
         <v>本次评估提示沟通存在明显阻力，核心变量是「${主要归因}」。处理重点不是先说服家长，而是先稳住情绪和事实边界，再决定沟通节奏。</v>
       </c>
       <c r="F4" t="str">
-        <v>可用占位符见 ⑩ 说明</v>
+        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
       </c>
       <c r="G4" t="str">
         <v>3</v>
@@ -493,30 +493,53 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>TPL_HS_DEFAULT</v>
+        <v>HOME_SCHOOL_TPL_B_SUMMARY</v>
       </c>
       <c r="B5" t="str">
         <v>home_school</v>
       </c>
       <c r="C5" t="str">
-        <v>green</v>
+        <v>B</v>
       </c>
       <c r="D5" t="str">
         <v>summary</v>
       </c>
       <c r="E5" t="str">
-        <v>当前家校关系状况良好，可按常规节奏沟通。保持日常的正向接触，让角色边界持续有储备。</v>
+        <v>本次评估显示沟通前需要一定铺垫，主要落在「${主要归因}」。建议先修复关系容器，积累两到三次正向接触后再谈具体问题。</v>
       </c>
       <c r="F5" t="str">
-        <v>兜底模板：命中未覆盖等级时使用</v>
+        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
       </c>
       <c r="G5" t="str">
-        <v>99</v>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>HOME_SCHOOL_TPL_A_SUMMARY</v>
+      </c>
+      <c r="B6" t="str">
+        <v>home_school</v>
+      </c>
+      <c r="C6" t="str">
+        <v>A</v>
+      </c>
+      <c r="D6" t="str">
+        <v>summary</v>
+      </c>
+      <c r="E6" t="str">
+        <v>当前家校关系状况良好，可按常规节奏沟通。保持日常的正向接触，让关系容器持续有储备。</v>
+      </c>
+      <c r="F6" t="str">
+        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
+      </c>
+      <c r="G6" t="str">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/business-libraries/test-data/home_school/output_template.xlsx
+++ b/business-libraries/test-data/home_school/output_template.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -424,22 +424,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>HOME_SCHOOL_TPL_E_SUMMARY</v>
+        <v>TPL_HS_RED_1</v>
       </c>
       <c r="B2" t="str">
         <v>home_school</v>
       </c>
       <c r="C2" t="str">
-        <v>E</v>
+        <v>red</v>
       </c>
       <c r="D2" t="str">
         <v>summary</v>
       </c>
       <c r="E2" t="str">
-        <v>本次评估触发 E 级保护通道，核心问题是「${主要归因}」。请立即停止单独沟通，保存全部记录并当天上报年级组长，后续由学校层面承接。</v>
+        <v>本次评估触发 5 级·极重（危机干预）：R 类红线已命中，核心风险是「${主要归因}」。请立即启动危机响应组——校长/分管校长指挥，德育主任现场协调，心理团队全员介入；班主任不再单独面对家长，只做信息汇总；遵守不独处、全留痕、不升级三原则，保护安全优先、控制损害，必要时联系法律顾问或警方。</v>
       </c>
       <c r="F2" t="str">
-        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
+        <v>可用占位符见 ⑩ 说明</v>
       </c>
       <c r="G2" t="str">
         <v>1</v>
@@ -447,22 +447,22 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>HOME_SCHOOL_TPL_D_SUMMARY</v>
+        <v>TPL_HS_ORANGE_2</v>
       </c>
       <c r="B3" t="str">
         <v>home_school</v>
       </c>
       <c r="C3" t="str">
-        <v>D</v>
+        <v>orange</v>
       </c>
       <c r="D3" t="str">
         <v>summary</v>
       </c>
       <c r="E3" t="str">
-        <v>本次沟通风险等级为 D 级，主要归因是「${主要归因}」，同时需关注「${次要归因}」。建议由年级组长陪同沟通并全程留痕。</v>
+        <v>本次评估判为 4 级·重度（强化干预），主要归因是「${主要归因}」。请组建强化干预组：心理团队+德育主任+管理层多方协作，班主任作为信息枢纽但不再单独面对家长；每周一次多方协作会，BPS 深度归因并形成家校关系诊断报告，班主任容器状态纳入评估；全程留痕。</v>
       </c>
       <c r="F3" t="str">
-        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
+        <v>可用占位符见 ⑩ 说明</v>
       </c>
       <c r="G3" t="str">
         <v>2</v>
@@ -470,22 +470,22 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>HOME_SCHOOL_TPL_C_SUMMARY</v>
+        <v>TPL_HS_YELLOW_3</v>
       </c>
       <c r="B4" t="str">
         <v>home_school</v>
       </c>
       <c r="C4" t="str">
-        <v>C</v>
+        <v>yellow</v>
       </c>
       <c r="D4" t="str">
         <v>summary</v>
       </c>
       <c r="E4" t="str">
-        <v>本次评估提示沟通存在明显阻力，核心变量是「${主要归因}」。处理重点不是先说服家长，而是先稳住情绪和事实边界，再决定沟通节奏。</v>
+        <v>本次评估判为 3 级·中度（定向干预），主要归因是「${主要归因}」。由心理教师主导专业介入，班主任负责日常执行，年级组长协调资源：先做 BPS 归因和容器评估，再走信任修复；处理重点不是先说服家长，而是先稳住情绪和事实边界。</v>
       </c>
       <c r="F4" t="str">
-        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
+        <v>可用占位符见 ⑩ 说明</v>
       </c>
       <c r="G4" t="str">
         <v>3</v>
@@ -493,22 +493,22 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>HOME_SCHOOL_TPL_B_SUMMARY</v>
+        <v>TPL_HS_BLUE_4</v>
       </c>
       <c r="B5" t="str">
         <v>home_school</v>
       </c>
       <c r="C5" t="str">
-        <v>B</v>
+        <v>blue</v>
       </c>
       <c r="D5" t="str">
         <v>summary</v>
       </c>
       <c r="E5" t="str">
-        <v>本次评估显示沟通前需要一定铺垫，主要落在「${主要归因}」。建议先修复关系容器，积累两到三次正向接触后再谈具体问题。</v>
+        <v>本次评估判为 2 级·轻度（普及干预），主要归因是「${主要归因}」。由班主任主导、年级组长支持：明确家校分工，用针对性沟通调整策略，修补信任小缺口；建立每周反馈节奏，跟进约定履行情况。</v>
       </c>
       <c r="F5" t="str">
-        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
+        <v>可用占位符见 ⑩ 说明</v>
       </c>
       <c r="G5" t="str">
         <v>4</v>
@@ -516,30 +516,53 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>HOME_SCHOOL_TPL_A_SUMMARY</v>
+        <v>TPL_HS_DEFAULT_5</v>
       </c>
       <c r="B6" t="str">
         <v>home_school</v>
       </c>
       <c r="C6" t="str">
-        <v>A</v>
+        <v>green</v>
       </c>
       <c r="D6" t="str">
         <v>summary</v>
       </c>
       <c r="E6" t="str">
-        <v>当前家校关系状况良好，可按常规节奏沟通。保持日常的正向接触，让关系容器持续有储备。</v>
+        <v>红线检查未命中任何 R 类红线，当前未发现需要危机干预的信号，可按常规节奏继续家校沟通；保持留痕与定期评估，出现红线信号时立即复评。</v>
       </c>
       <c r="F6" t="str">
-        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
+        <v>可用占位符见 ⑩ 说明</v>
       </c>
       <c r="G6" t="str">
         <v>5</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>TPL_HS_DEFAULT</v>
+      </c>
+      <c r="B7" t="str">
+        <v>home_school</v>
+      </c>
+      <c r="C7" t="str">
+        <v>green</v>
+      </c>
+      <c r="D7" t="str">
+        <v>summary</v>
+      </c>
+      <c r="E7" t="str">
+        <v>当前家校关系处于 1 级·关注水平：六维度均分健康，未触发分级干预，未命中 R 类红线。保持基础预防——每周固定反馈、主动分享正面信息、及时回应；每月做一次沟通质量自检，出现红线信号时立即复评。</v>
+      </c>
+      <c r="F7" t="str">
+        <v>兜底模板：命中未覆盖等级时使用</v>
+      </c>
+      <c r="G7" t="str">
+        <v>99</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G7"/>
   </ignoredErrors>
 </worksheet>
 </file>